--- a/content/Question Bank/Coding Questions/Unit 13 - Debugging/Unit 13 - Debugging - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 13 - Debugging/Unit 13 - Debugging - Coding Questions.xlsx
@@ -596,13 +596,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A common off-by-one bug: count how many whole numbers there are from A to B, including both ends. Read A and B and print the count.
+          <t xml:space="preserve">
+Rohit wrote code to count how many days the college fest runs from day A to day B, but his answer was always one short — the classic off-by-one bug, because subtracting forgets to include the last day. Write the correct version: read A and B from one line and print how many whole numbers there are from A to B, including both ends.
 ### Input Format
 - Line 1: 'A B'
 ### Output Format
 ```
 5
 ```
+### Example Walkthrough
+For A=1 and B=5, the numbers are 1, 2, 3, 4, 5 — that is 5 numbers, not the 4 that B - A would give. The inclusive count is B - A + 1 = 5, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -740,13 +743,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Read two numbers. Use an assert to confirm the second is not zero (a sanity check), then print the first divided by the second.
+          <t xml:space="preserve">
+Kavya computes her scooter's mileage by dividing distance travelled by fuel used, and she wants her program to stop loudly if the fuel value is ever zero — the kind of sanity check programmers call an assertion. Write a program that reads two numbers from one line, uses `assert` to confirm the second is not zero, and then prints the first divided by the second.
 ### Input Format
 - Line 1: 'a b' (b is never zero)
 ### Output Format
 ```
 5.0
 ```
+### Example Walkthrough
+The sample inputs are 10 and 2. The assert checks that 2 is not zero and passes silently, so the program continues and prints 10 / 2, which is `5.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -885,13 +891,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A buggy average often uses integer division by mistake. Read a line of numbers and print their true average rounded to 2 decimal places.
+          <t xml:space="preserve">
+Aman's friend wrote a marks-average calculator, but it kept giving strange answers like 1 instead of 1.5 — he had used integer division (//), which throws away the decimal part. Write the correct version: read a line of space-separated numbers and print their true average, rounded to 2 decimal places.
 ### Input Format
 - Line 1: Space-separated numbers
 ### Output Format
 ```
 1.5
 ```
+### Example Walkthrough
+The sample numbers are 1 and 2, so the sum is 3 and the count is 2. True division gives 3 / 2 = 1.5 (integer division would wrongly give 1), so the program prints `1.5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1029,13 +1038,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Read a number and print 'Even' or 'Odd'. Remember that 0 is even.
+          <t xml:space="preserve">
+The hostel mess serves special dosa to even-numbered rooms on Sundays, so Vikram wrote a quick even/odd checker — but his first version wrongly treated 0 as odd. Write the correct program: read a number and print 'Even' if it is divisible by 2, and 'Odd' otherwise. Remember that 0 is even.
 ### Input Format
 - Line 1: A number
 ### Output Format
 ```
 Even
 ```
+### Example Walkthrough
+The sample input is 4, and 4 % 2 equals 0, meaning 4 divides evenly by 2. So the program prints `Even`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1173,13 +1185,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A classic bug initialises the maximum to 0, which fails when all values are negative. Read a line of numbers and print the true maximum.
+          <t xml:space="preserve">
+On a winter trek, Neha logged the temperature every hour and asked her program for the warmest reading — but it printed 0, a temperature that never occurred! The bug: her code started the maximum at 0, which fails when every value is negative. Write the correct version: read a line of space-separated numbers and print the true maximum.
 ### Input Format
 - Line 1: Space-separated numbers
 ### Output Format
 ```
 -1
 ```
+### Example Walkthrough
+The readings are -3, -1, and -2 — all negative. Starting the maximum from the first value and comparing each number in turn, the largest is `-1` (a buggy start at 0 would wrongly print 0).
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1321,7 +1336,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Read a sorted line of numbers and a target. Use an assert to confirm the list really is sorted, then print 'Found' if the target is present and 'Not Found' otherwise.
+          <t xml:space="preserve">
+The library keeps issued-book IDs in a sorted list so lookups stay fast, and Sameer wants his search program to fail loudly if the list ever arrives unsorted — a perfect job for assert. Write a program that reads a line of sorted numbers and then a target. First use assert to confirm each number is at least as large as the one before it, then print 'Found' if the target is present and 'Not Found' otherwise.
 ### Input Format
 - Line 1: Sorted space-separated numbers
 - Line 2: Target
@@ -1329,6 +1345,8 @@
 ```
 Found
 ```
+### Example Walkthrough
+The list `1 2 3 4 5` passes the sorted check, since each value is at least as large as the one before it. The target 3 does appear in the list, so the program prints `Found`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1475,13 +1493,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Read a whole number and print 'Yes' if its digits read the same forwards and backwards, otherwise 'No'. A single-digit number counts as a palindrome.
+          <t xml:space="preserve">
+On the bus ride home, Ritu and her friends play a game: a ticket number is 'lucky' if it reads the same forwards and backwards, like 121. Write a program that reads a whole number and prints 'Yes' if its digits form such a palindrome, and 'No' otherwise. A single-digit number always counts as a palindrome.
 ### Input Format
 - Line 1: A whole number
 ### Output Format
 ```
 Yes
 ```
+### Example Walkthrough
+The sample number 121 read backwards is still 121 — the first and last digits are both 1 and the middle digit stays 2 — so the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1619,7 +1640,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Simulate a stack with N operations ('push' or 'pop'). Use an assert to guarantee you never pop an empty stack (the input is well-formed), then print the final number of items on the stack.
+          <t xml:space="preserve">
+In the mess kitchen, clean plates are stacked up: 'push' places a plate on top and 'pop' takes one off. Taking a plate from an empty stack is impossible, and Arnav wants an assert to guarantee his simulation never tries it. Write a program that reads N and then N operations ('push' or 'pop'). Use assert to check the stack is not empty before every pop (the input is well-formed), then print how many plates remain at the end.
 ### Input Format
 - Line 1: N
 - Next N lines: 'push' or 'pop'
@@ -1627,6 +1649,8 @@
 ```
 2
 ```
+### Example Walkthrough
+The 4 sample operations are push, push, pop, push. The plate count goes 1, 2, back down to 1, then up to 2 — and no pop ever hits an empty stack — so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1793,13 +1817,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Read a line of numbers (which may be negative) and print the largest sum of any run of one or more consecutive numbers.
+          <t xml:space="preserve">
+Dhruv tracks his cricket team's net runs per over — positive when they scored freely, negative when wickets fell cheaply — and wants to find the team's best stretch of consecutive overs. Write a program that reads a line of numbers (which may be negative) and prints the largest sum of any run of one or more consecutive numbers.
 ### Input Format
 - Line 1: Space-separated numbers
 ### Output Format
 ```
 6
 ```
+### Example Walkthrough
+In `-2 1 -3 4 -1 2 1 -5 4`, the best consecutive stretch is `4 -1 2 1`, which adds up to 6. No other run of neighbouring numbers does better, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1941,13 +1968,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Implement the leap-year rules yourself (a common source of bugs): a year is a leap year if it is divisible by 4, except years divisible by 100 are not, unless they are also divisible by 400. Read a year and print 'Yes' or 'No'.
+          <t xml:space="preserve">
+Zara's cousin was born on 29 February, so his 'real' birthday only arrives in a leap year — and Zara's first program got years like 1900 wrong. Implement the full rules yourself (a common source of bugs): a year is a leap year if it is divisible by 4, except that years divisible by 100 are not, unless they are also divisible by 400. Read a year and print 'Yes' or 'No'.
 ### Input Format
 - Line 1: A year
 ### Output Format
 ```
 Yes
 ```
+### Example Walkthrough
+2000 is divisible by 4, and also by 100 — which would normally disqualify it — but it is divisible by 400 too, so the exception-to-the-exception applies and the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 13 - Debugging/Unit 13 - Debugging - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 13 - Debugging/Unit 13 - Debugging - Coding Questions.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,12 +624,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -636,7 +649,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>edge-cases</t>
+          <t>debugging-techniques</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -768,12 +781,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -916,12 +939,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -931,7 +964,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>edge-cases</t>
+          <t>debugging-techniques</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1063,12 +1096,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,7 +1121,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>edge-cases</t>
+          <t>debugging-techniques</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1210,12 +1253,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1225,7 +1278,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>edge-cases</t>
+          <t>debugging-techniques</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1362,12 +1415,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1518,12 +1581,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1533,7 +1606,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>edge-cases</t>
+          <t>debugging-techniques</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1666,12 +1739,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1812,10 +1895,523 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Python - Inclusive Loop Fix</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Inclusive Loop Fix. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+1
+2
+3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>debugging</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1
+2
+3</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1
+2
+3
+4
+5</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1
+2
+3
+4
+5
+6
+7</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1
+2</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>1
+2
+3
+4
+5
+6
+7
+8
+9
+10</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>n=int(input())
+for i in range(1,n+1): print(i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Average Formula Fix</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Average Formula Fix. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Integers
+### Output Format
+```
+2.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>debugging</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1 2 3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0 10</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-1 1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10 20 30 40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>7 7</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>100 -100 50</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>16.666666666666668</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>nums=list(map(int,input().split())); print(sum(nums)/len(nums))</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Python - Max Subarray Sum</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Dhruv tracks his cricket team's net runs per over — positive when they scored freely, negative when wickets fell cheaply — and wants to find the team's best stretch of consecutive overs. Write a program that reads a line of numbers (which may be negative) and prints the largest sum of any run of one or more consecutive numbers.
@@ -1832,124 +2428,134 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>-2 1 -3 4 -1 2 1 -5 4</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>-1 2 -1 2 -1</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 best = current = nums[0]
@@ -1960,13 +2566,13 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Leap Year Rules</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Zara's cousin was born on 29 February, so his 'real' birthday only arrives in a leap year — and Zara's first program got years like 1900 wrong. Implement the full rules yourself (a common source of bugs): a year is a leap year if it is divisible by 4, except that years divisible by 100 are not, unless they are also divisible by 400. Read a year and print 'Yes' or 'No'.
@@ -1983,124 +2589,134 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>validation</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>1900</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>2100</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>year = int(input())
 if year % 400 == 0:
@@ -2115,13 +2731,13 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Sum of Inclusive Range</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read A and B and print the sum of every whole number from A to B, including both A and B.
 ### Input Format
@@ -2130,142 +2746,154 @@
 ```
 15
 ```
+### Example Walkthrough
+In the sample, `A` is `1` and `B` is `5`. Summing every whole number from `1` to `5` gives `15`, so the program prints `15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>1 5</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>3 3</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>1 10</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>-5 -1</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>-3 3</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>a, b = map(int, input().split())
 print(sum(range(a, b + 1)))</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Last Valid Index</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>A list of length n has valid indexes 0 to n-1. Read a line of values and print the last valid index.
 ### Input Format
@@ -2274,142 +2902,154 @@
 ```
 2
 ```
+### Example Walkthrough
+In the sample, the values are `a b c`. With `3` items, the valid indexes are `0`, `1`, and `2`, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>1</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>-1 -2</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>a b c d</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>items = input().split()
 print(len(items) - 1)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Boundary Pass Mark</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>The pass mark is 40 and exactly 40 passes. Read a score and print 'Pass' if it is 40 or more, otherwise 'Fail'.
 ### Input Format
@@ -2418,142 +3058,154 @@
 ```
 Pass
 ```
+### Example Walkthrough
+In the sample, the score is exactly `40`, the pass mark itself. Since `40 &gt;= 40`, the program prints `Pass`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>score = int(input())
 print("Pass" if score &gt;= 40 else "Fail")</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Count Up Correctly</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Print every number from 1 to N, including N, separated by spaces (getting the loop bounds right).
 ### Input Format
@@ -2562,137 +3214,149 @@
 ```
 1 2 3 4 5
 ```
+### Example Walkthrough
+In the sample, `N` is `5`. Counting up to and including `5` gives `1 2 3 4 5`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R15" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>n = int(input())
 print(*range(1, n + 1))</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Equal or Larger</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read two numbers. Print 'Equal' if they are equal; otherwise print the larger one. (Watch the boundary where they are equal.)
 ### Input Format
@@ -2701,129 +3365,141 @@
 ```
 Equal
 ```
+### Example Walkthrough
+In the sample, both numbers are `5`. Since they are equal, the program prints `Equal` rather than either value.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>3 3</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>5 2</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1 4</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>-5 -5</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>-1 1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>100 99</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>a, b = map(int, input().split())
 if a == b:
@@ -2833,13 +3509,13 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Assert Non-Empty</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Read a word. Use an assert to confirm it is not empty, then print its first character.
 ### Input Format
@@ -2848,129 +3524,141 @@
 ```
 h
 ```
+### Example Walkthrough
+In the sample, the word is `hello`, which is not empty, so the assert passes and the program prints its first character, `h`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>assertions</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>1</v>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>xyz</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>w</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>banana</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>word = input()
 assert len(word) &gt; 0, "word must not be empty"
@@ -2978,13 +3666,507 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Assert Positive</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Assert Positive. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Number
+### Output Format
+```
+OK
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>debugging</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>assertions</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Not positive</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Not positive</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Not positive</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>try:
+ n=int(input()); assert n&gt;0; print("OK")
+except AssertionError: print("Not positive")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Boundary Pass Fix</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Boundary Pass Fix. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Marks
+### Output Format
+```
+Pass
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>debugging</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>m=int(input()); print("Pass" if m&gt;=40 else "Fail")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Correct Percentage</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Read marks obtained and the total marks, and print the percentage rounded to 1 decimal place (avoiding the integer-division bug).
 ### Input Format
@@ -2993,142 +4175,154 @@
 ```
 90.0
 ```
+### Example Walkthrough
+In the sample, the marks obtained are `90` out of `100`. The percentage is `90 / 100 x 100 = 90.0`, so the program prints `90.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>45 50</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1 3</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>33.3</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>50 50</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0 50</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>50 200</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>33 99</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>33.3</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>obtained, total = map(int, input().split())
 print(round(obtained / total * 100, 1))</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Grade Boundaries</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Read a mark and print its grade using inclusive boundaries: 'A' for 90 or more, 'B' for 75 or more, 'C' for 60 or more, and 'F' otherwise. Check the exact boundary values.
 ### Input Format
@@ -3137,129 +4331,141 @@
 ```
 A
 ```
+### Example Walkthrough
+In the sample, the mark is exactly `90`, the boundary for an `A`. Since `90 &gt;= 90`, the program prints `A`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>1</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>marks = int(input())
 if marks &gt;= 90:
@@ -3273,13 +4479,13 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Sum of Squares</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>A buggy version adds the numbers instead of their squares. Read a line of numbers and print the sum of their squares.
 ### Input Format
@@ -3288,142 +4494,154 @@
 ```
 14
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3`. Their squares are `1`, `4`, and `9`, which sum to `14`, so the program prints `14`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>2 4</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>-3 3</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 print(sum(x * x for x in nums))</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Above Average Count</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read a line of numbers and print how many of them are strictly greater than the average of the list.
 ### Input Format
@@ -3432,129 +4650,141 @@
 ```
 2
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 4 5`, with an average of `3`. The values `4` and `5` are strictly greater than `3`, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>1</v>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1 10</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>-5 -1 5</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>1 1 1 1 1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 average = sum(nums) / len(nums)
@@ -3562,13 +4792,13 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Reverse Without Loss</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read a line of values and print them reversed, making sure not to drop the first or last element.
 ### Input Format
@@ -3577,142 +4807,154 @@
 ```
 3 2 1
 ```
+### Example Walkthrough
+In the sample, the values are `1 2 3`. Reversed, they become `3 2 1`, which the program prints, keeping both the first and last elements.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>1</v>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>3 2 1</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>2 1</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>5 4 3 2 1</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>x y</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>y x</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>9 8 7 6</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>6 7 8 9</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>items = input().split()
 print(*items[::-1])</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Smallest Gap</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read a line of numbers, sort them, and print the smallest difference between any two neighbouring values in the sorted order.
 ### Input Format
@@ -3721,129 +4963,141 @@
 ```
 0
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 1 3`. Sorted, they are `1, 1, 3`, and the gaps between neighbours are `0` and `2`. The smallest gap is `0`, so the program prints `0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>3 1 4 1 5</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>10 20 30</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>5 8</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>-5 5</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>-10 -3 -7</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0 0 0</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>nums = sorted(map(int, input().split()))
 smallest = nums[1] - nums[0]
@@ -3855,13 +5109,13 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Assert Valid Marks</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read a line of marks. Use an assert to confirm every mark is between 0 and 100, then print their average rounded to 1 decimal place.
 ### Input Format
@@ -3870,129 +5124,141 @@
 ```
 90.0
 ```
+### Example Walkthrough
+In the sample, the marks are `90 90 90`, all within `0` to `100`, so the assert passes and the average, `90.0`, is printed.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>assertions</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>80 90 100</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>0 100</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>60 70 80 90</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>marks = list(map(int, input().split()))
 assert all(0 &lt;= m &lt;= 100 for m in marks), "marks out of range"
@@ -4000,13 +5266,680 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Sorted Assertion</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Sorted Assertion. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Integers
+### Output Format
+```
+Sorted
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>debugging</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>assertions</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1 2 3</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Sorted</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3 2 1</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Not sorted</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1 1 2</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sorted</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Sorted</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>-1 0 1</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Sorted</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1 3 2</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Not sorted</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0 0 0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Sorted</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>nums=list(map(int,input().split()))
+try: assert nums==sorted(nums); print("Sorted")
+except AssertionError: print("Not sorted")</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - First Zero Trace</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for First Zero Trace. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Integers
+### Output Format
+```
+1
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>debugging</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>debugging-workflow</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1 0 2</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1 2 3</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5 4 0 0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>-1 0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>9 8 7</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0 1 0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>ans=-1
+for i,x in enumerate(map(int,input().split())):
+ if x==0: ans=i; break
+print(ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Logging Level Count</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Logging Level Count. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: Log level
+### Output Format
+```
+2
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>debugging</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>logging</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3
+INFO
+ERROR
+ERROR</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1
+INFO</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2
+ERROR
+WARN</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>4
+ERROR
+ERROR
+ERROR
+INFO</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2
+error
+ERROR</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1
+ERROR</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>n=int(input()); c=0
+for _ in range(n):
+ if input()=="ERROR": c+=1
+print(c)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Pair Sum Exists</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Read a sorted line of numbers and a target. Print 'Yes' if some pair of different positions adds up to the target, otherwise 'No'. Use two indexes moving inward and mind the boundaries.
 ### Input Format
@@ -4016,136 +5949,148 @@
 ```
 Yes
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 4 5` and the target is `6`. The pair `1` and `5` adds up to `6`, so the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>1</v>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>1 2 3 4
 5</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1 2 3
 7</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>2 4
 6</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>1 2
 3</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>-5 -1 0 3
 -6</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6
 11</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>-3 -2 -1
 -3</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 target = int(input())
@@ -4164,13 +6109,13 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Max Window Sum</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Read a line of numbers and a window size K. Print the largest sum of any K consecutive numbers. Take care that the last window is included.
 ### Input Format
@@ -4180,136 +6125,148 @@
 ```
 9
 ```
+### Example Walkthrough
+In the sample, the numbers are `4 5` and `K` is `2`. The only window of size `2` sums to `4 + 5 = 9`, so the program prints `9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>1</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 2</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>5 1 1
 1</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>2 2 2
 3</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>-1 -2 -3
 1</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>5
 1</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>1 2 3 4
 4</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>-5 10 -3 8
 2</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 k = int(input())
@@ -4322,13 +6279,13 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Careful Rounding</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Floating-point sums can look wrong (0.1 + 0.2 is not exactly 0.3). Read a line of decimal amounts and print their total rounded to 2 decimal places.
 ### Input Format
@@ -4337,142 +6294,154 @@
 ```
 0.3
 ```
+### Example Walkthrough
+In the sample, the amounts are `0.1` and `0.2`. Their sum, rounded to 2 decimal places, is `0.3`, so the program prints `0.3` even though raw floating-point addition can look slightly off.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>0.1 0.2</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>1.5 2.5</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>0.01 0.02</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>-1.5 1.5</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>10.999 0.001</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>-0.1 -0.2</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>-0.3</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>amounts = list(map(float, input().split()))
 print(round(sum(amounts), 2))</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Count All Vowels</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>A buggy counter resets between words and loses the total. Read a sentence and print the total number of vowels across the whole sentence, ignoring case.
 ### Input Format
@@ -4481,129 +6450,141 @@
 ```
 4
 ```
+### Example Walkthrough
+In the sample, the sentence is `the quick fox`. It contains `4` vowels (`e`, `u`, `i`, `o`), so the program prints `4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>1</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>the quick brown</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>aeiou</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>xyz</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>AEIOU</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>b c d</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Hello World</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>sentence = input().lower()
 count = 0
@@ -4614,13 +6595,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - First Repeated Value</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read a line of numbers and print the first value whose second occurrence appears earliest as you scan left to right. If nothing repeats, print 'None'.
 ### Input Format
@@ -4629,129 +6610,141 @@
 ```
 2
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 2 1`. Scanning left to right, `2` is the first value seen a second time, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>1 2 3 2 1</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>5 6 7</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>4 4</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>-3 -3</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>9 8 7 6 8</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>nums = input().split()
 seen = set()
@@ -4765,13 +6758,13 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Assert Then Factorial</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read a number. Use an assert to confirm it is not negative (factorial is undefined for negatives), then compute and print its factorial.
 ### Input Format
@@ -4780,129 +6773,141 @@
 ```
 120
 ```
+### Example Walkthrough
+In the sample, the number is `5`, which is not negative, so the assert passes and the program prints `5! = 120`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>assertions</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>3628800</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>n = int(input())
 assert n &gt;= 0, "factorial needs a non-negative number"
@@ -4913,13 +6918,13 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Collatz Steps</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read a number and count how many steps it takes to reach 1 using the Collatz process: if the number is even, halve it; if odd, triple it and add one. Print the number of steps (0 if the number is already 1).
 ### Input Format
@@ -4928,129 +6933,141 @@
 ```
 8
 ```
+### Example Walkthrough
+In the sample, the number is `6`. Following the Collatz process gives `6, 3, 10, 5, 16, 8, 4, 2, 1`, which takes `8` steps to reach `1`, so the program prints `8`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>edge-cases</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>1</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>n = int(input())
 steps = 0
@@ -5064,6 +7081,495 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Off By One Window</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Off By One Window. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Integers
+- Line 2: K
+### Output Format
+```
+7
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>debugging</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>debugging-techniques</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1 2 3 4
+2</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5
+1</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1 2 3
+3</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-1 -2 -3
+2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10 0 10
+2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1 1 1 1
+3</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>5 4 3 2 1
+2</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>nums=list(map(int,input().split())); k=int(input()); best=sum(nums[:k])
+for i in range(1,len(nums)-k+1): best=max(best,sum(nums[i:i+k]))
+print(best)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Invariant Stack</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Invariant Stack. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Operations
+### Output Format
+```
+OK
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>debugging</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>assertions</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>push pop</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Broken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>push push pop</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>push pop pop</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Broken</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>push push pop pop</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>push pop push pop</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>ops=input().split(); stack=[]; ok=True
+for op in ops:
+ if op=="push": stack.append(1)
+ elif op=="pop":
+  if not stack: ok=False; break
+  stack.pop()
+print("OK" if ok else "Broken")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Rubber Duck Trace</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Rubber Duck Trace. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Integers
+### Output Format
+```
+1
+3
+6
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>debugging</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>debugging-workflow</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1 2 3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1
+3
+6</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-1 1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-1
+0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0 0 0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0
+0
+0</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10 -3 2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>10
+7
+9</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1 -2 -3</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1
+-1
+-4</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>100 200</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>100
+300</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>total=0
+for x in map(int,input().split()):
+ total+=x; print(total)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/Question Bank/Coding Questions/Unit 13 - Debugging/Unit 13 - Debugging - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 13 - Debugging/Unit 13 - Debugging - Coding Questions.xlsx
@@ -1900,7 +1900,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Inclusive Loop Fix. Read the input values and print the required result exactly.
+          <t>A ticket-numbering script should print every ticket number from 1 to N, one per line, but a common off-by-one bug is writing the loop as `range(1, n)`, which stops one short and misses ticket N entirely. Write the correct version.
+Write a program that reads a whole number N and prints every whole number from 1 to N, inclusive, one per line, using `range(1, n + 1)`. If N is 0 or less, print nothing.
 ### Input Format
 - Line 1: N
 ### Output Format
@@ -1909,9 +1910,11 @@
 2
 3
 ```
+### Example Walkthrough
+In the sample, N is 3. The correct range `range(1, 4)` produces 1, 2, and 3, so the program prints all three, including the final ticket number 3 that the buggy `range(1, 3)` would have missed.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1998,7 +2001,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
           <t>5</t>
@@ -2074,16 +2076,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Average Formula Fix. Read the input values and print the required result exactly.
+          <t>A grading script computes the class average from a list of scores, but a common bug is dividing the sum by the wrong count, such as a hardcoded number of students, instead of the actual number of scores that were entered. Write the correct version.
+Write a program that reads a line of space-separated numbers and prints their average, computed as the sum of the numbers divided by exactly how many numbers were entered.
 ### Input Format
-- Line 1: Integers
+- Line 1: Space-separated numbers
 ### Output Format
 ```
 2.0
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3`. Their sum is 6 and there are 3 of them, so the average is 6 / 3 = 2.0, which the program prints.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3674,16 +3679,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Assert Positive. Read the input values and print the required result exactly.
+          <t>A configuration loader uses an assertion to guarantee that a setting value is a positive number before continuing, catching the resulting `AssertionError` to report a friendly message instead of letting the program crash with a raw traceback.
+Write a program that reads a whole number inside a `try` block, uses `assert n &gt; 0` to check it is positive, and prints `OK` if the assertion passes. If the assertion fails, catch the `AssertionError` and print `Not positive`.
 ### Input Format
-- Line 1: Number
+- Line 1: A whole number
 ### Output Format
 ```
 OK
 ```
+### Example Walkthrough
+In the sample, the number is 1, which is positive, so the assertion passes and the program prints `OK`. A value of `0` or lower would fail the assertion and print `Not positive` instead.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3829,16 +3837,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Boundary Pass Fix. Read the input values and print the required result exactly.
+          <t>A results checker marks students as passing at exactly 40 marks or above, but a common bug is using `&gt;` instead of `&gt;=`, which would incorrectly fail a student who scored exactly 40. Write the correct version.
+Write a program that reads a whole number of marks and prints `Pass` if the marks are 40 or more (using `&gt;=`, so exactly 40 counts as a pass), and `Fail` otherwise.
 ### Input Format
 - Line 1: Marks
 ### Output Format
 ```
 Pass
 ```
+### Example Walkthrough
+In the sample, the marks are exactly 40. Using `&gt;=`, 40 is greater than or equal to 40, so the program prints `Pass`, unlike a buggy `&gt;` check which would have incorrectly printed `Fail`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5274,16 +5285,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Sorted Assertion. Read the input values and print the required result exactly.
+          <t>A leaderboard update script assumes an incoming list of scores is already sorted before merging it with the existing leaderboard, and uses an assertion to immediately catch the moment that assumption is violated instead of silently producing a broken leaderboard.
+Write a program that reads a line of space-separated whole numbers inside a `try` block, uses `assert nums == sorted(nums)` to check the list is sorted from smallest to largest, and prints `Sorted` if the assertion passes. If it fails, catch the `AssertionError` and print `Not sorted`.
 ### Input Format
-- Line 1: Integers
+- Line 1: Space-separated whole numbers
 ### Output Format
 ```
 Sorted
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3`, which are already in increasing order, so the assertion passes and the program prints `Sorted`. Numbers like `3 2 1` would fail the assertion and print `Not sorted` instead.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5429,16 +5443,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for First Zero Trace. Read the input values and print the required result exactly.
+          <t>A sensor log analyzer needs to find the position of the first zero reading in a batch, since a zero often indicates the sensor briefly disconnected, so an engineer traces through the values to find the index of the first occurrence, or -1 if none of the readings were zero.
+Write a program that reads a line of space-separated whole numbers and prints the index (starting at 0) of the first value equal to 0. If no value is 0, print `-1`.
 ### Input Format
-- Line 1: Integers
+- Line 1: Space-separated whole numbers
 ### Output Format
 ```
 1
 ```
+### Example Walkthrough
+In the sample, the readings are `1 0 2`. The first 0 appears at index 1 (the second position, counting from 0), so the program prints `1`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5585,17 +5602,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Logging Level Count. Read the input values and print the required result exactly.
+          <t>A log-monitoring dashboard scans a batch of log entries and counts exactly how many are tagged with the level `ERROR` (matching the exact case used by the logging system, so `error` in lower case does not count), so it can flag a spike in errors.
+Write a program that reads a whole number N, then reads N more lines each containing a log level, and prints how many of them are exactly `ERROR`.
 ### Input Format
-- Line 1: N
-- Next N lines: Log level
+- Line 1: N, the number of log entries
+- Next N lines: a log level each
 ### Output Format
 ```
 2
 ```
+### Example Walkthrough
+In the sample, N is 3 with the levels `INFO`, `ERROR`, and `ERROR`. Two of the three entries are exactly `ERROR`, so the program prints `2`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- N is a valid whole number matching the number of lines that follow.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -7089,17 +7109,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Off By One Window. Read the input values and print the required result exactly.
+          <t>A stock-analysis tool finds the best K-day rolling sum of daily profits to spot the strongest short streak, sliding a window of size K across the data. A common off-by-one bug stops the sliding window one position too early and misses the very last possible window; write the correct version.
+Write a program that reads a line of space-separated whole numbers, reads a whole number K on the next line, and prints the maximum sum of any K consecutive numbers in the list, making sure to check every possible window including the last one.
 ### Input Format
-- Line 1: Integers
-- Line 2: K
+- Line 1: Space-separated whole numbers
+- Line 2: K, the window size
 ### Output Format
 ```
 7
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 4` and K is 2. The possible windows of size 2 are `1+2=3`, `2+3=5`, and `3+4=7`; the largest is 7, so the program prints `7`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- K is a valid whole number no greater than the number of values given.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7252,16 +7275,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Invariant Stack. Read the input values and print the required result exactly.
+          <t>A browser's back-button history is modeled as a stack of push and pop operations coming from user navigation actions. The invariant that must always hold is that you can't pop when the stack is empty (you can't go back further than the history allows), so the app validates a sequence of operations to check whether it ever breaks that rule.
+Write a program that reads a line of space-separated operations (`push` or `pop`), simulates them on a stack, and prints `OK` if every `pop` had something to remove, or `Broken` the moment a `pop` is attempted on an empty stack.
 ### Input Format
-- Line 1: Operations
+- Line 1: Space-separated operations (`push` or `pop`)
 ### Output Format
 ```
 OK
 ```
+### Example Walkthrough
+In the sample, the operations are `push pop`. The `push` adds an item, and the `pop` removes it since the stack wasn't empty, so the invariant holds and the program prints `OK`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a valid line of space-separated operations, each either `push` or `pop`.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7411,18 +7437,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Rubber Duck Trace. Read the input values and print the required result exactly.
+          <t>While rubber-duck debugging a budgeting script, a developer traces through it line by line: for each new expense added, print the running total so far immediately, to see exactly where the total starts to go wrong.
+Write a program that reads a line of space-separated whole numbers and, keeping a running total, prints the total after adding each number, one line per number.
 ### Input Format
-- Line 1: Integers
+- Line 1: Space-separated whole numbers
 ### Output Format
 ```
 1
 3
 6
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3`. After adding 1, the running total is 1; after adding 2, it becomes 3; after adding 3, it becomes 6 - so the program prints `1`, then `3`, then `6`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 13 - Debugging/Unit 13 - Debugging - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 13 - Debugging/Unit 13 - Debugging - Coding Questions.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - Coding - Unit 13" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,19 +596,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Rohit wrote code to count how many days the college fest runs from day A to day B, but his answer was always one short — the classic off-by-one bug, because subtracting forgets to include the last day. Write the correct version: read A and B from one line and print how many whole numbers there are from A to B, including both ends.
-### Input Format
-- Line 1: 'A B'
-### Output Format
-```
-5
-```
+          <t>Rohit wrote code to count how many days the college fest runs from day A to day B, but his answer was always one short — the classic off-by-one bug, because subtracting forgets to include the last day. Write the correct version: read A and B from one line and print how many whole numbers there are from A to B, including both ends.
 ### Example Walkthrough
 For A=1 and B=5, the numbers are 1, 2, 3, 4, 5 — that is 5 numbers, not the 4 that B - A would give. The inclusive count is B - A + 1 = 5, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -744,7 +734,7 @@
       <c r="AG2" t="inlineStr">
         <is>
           <t>a, b = map(int, input().split())
-print(b - a + 1)</t>
+print(b - a + 1)  # +1 makes the count inclusive of both endpoints</t>
         </is>
       </c>
     </row>
@@ -756,19 +746,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Kavya computes her scooter's mileage by dividing distance travelled by fuel used, and she wants her program to stop loudly if the fuel value is ever zero — the kind of sanity check programmers call an assertion. Write a program that reads two numbers from one line, uses `assert` to confirm the second is not zero, and then prints the first divided by the second.
-### Input Format
-- Line 1: 'a b' (b is never zero)
-### Output Format
-```
-5.0
-```
+          <t>Kavya computes her scooter's mileage by dividing distance travelled by fuel used, and she wants her program to stop loudly if the fuel value is ever zero — the kind of sanity check programmers call an assertion. Write a program that reads two numbers from one line, uses `assert` to confirm the second is not zero, and then prints the first divided by the second.
 ### Example Walkthrough
 The sample inputs are 10 and 2. The assert checks that 2 is not zero and passes silently, so the program continues and prints 10 / 2, which is `5.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -901,7 +884,7 @@
       <c r="AG3" t="inlineStr">
         <is>
           <t>a, b = map(int, input().split())
-assert b != 0, "divisor must be non-zero"
+assert b != 0, "divisor must be non-zero"  # fail loudly instead of dividing by zero
 print(a / b)</t>
         </is>
       </c>
@@ -914,19 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Aman's friend wrote a marks-average calculator, but it kept giving strange answers like 1 instead of 1.5 — he had used integer division (//), which throws away the decimal part. Write the correct version: read a line of space-separated numbers and print their true average, rounded to 2 decimal places.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-1.5
-```
+          <t>Aman's friend wrote a marks-average calculator, but it kept giving strange answers like 1 instead of 1.5 — he had used integer division (//), which throws away the decimal part. Write the correct version: read a line of space-separated numbers and print their true average, rounded to 2 decimal places.
 ### Example Walkthrough
 The sample numbers are 1 and 2, so the sum is 3 and the count is 2. True division gives 3 / 2 = 1.5 (integer division would wrongly give 1), so the program prints `1.5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1059,7 +1035,7 @@
       <c r="AG4" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-print(round(sum(nums) / len(nums), 2))</t>
+print(round(sum(nums) / len(nums), 2))  # true division keeps the decimal, unlike //</t>
         </is>
       </c>
     </row>
@@ -1071,19 +1047,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-The hostel mess serves special dosa to even-numbered rooms on Sundays, so Vikram wrote a quick even/odd checker — but his first version wrongly treated 0 as odd. Write the correct program: read a number and print 'Even' if it is divisible by 2, and 'Odd' otherwise. Remember that 0 is even.
-### Input Format
-- Line 1: A number
-### Output Format
-```
-Even
-```
+          <t>The hostel mess serves special dosa to even-numbered rooms on Sundays, so Vikram wrote a quick even/odd checker — but his first version wrongly treated 0 as odd. Write the correct program: read a number and print 'Even' if it is divisible by 2, and 'Odd' otherwise. Remember that 0 is even.
 ### Example Walkthrough
 The sample input is 4, and 4 % 2 equals 0, meaning 4 divides evenly by 2. So the program prints `Even`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1216,7 +1185,7 @@
       <c r="AG5" t="inlineStr">
         <is>
           <t>n = int(input())
-print("Even" if n % 2 == 0 else "Odd")</t>
+print("Even" if n % 2 == 0 else "Odd")  # 0 % 2 == 0, so zero is correctly treated as even</t>
         </is>
       </c>
     </row>
@@ -1228,19 +1197,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-On a winter trek, Neha logged the temperature every hour and asked her program for the warmest reading — but it printed 0, a temperature that never occurred! The bug: her code started the maximum at 0, which fails when every value is negative. Write the correct version: read a line of space-separated numbers and print the true maximum.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
--1
-```
+          <t>On a winter trek, Neha logged the temperature every hour and asked her program for the warmest reading — but it printed 0, a temperature that never occurred! The bug: her code started the maximum at 0, which fails when every value is negative. Write the correct version: read a line of space-separated numbers and print the true maximum.
 ### Example Walkthrough
 The readings are -3, -1, and -2 — all negative. Starting the maximum from the first value and comparing each number in turn, the largest is `-1` (a buggy start at 0 would wrongly print 0).
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1373,7 +1335,7 @@
       <c r="AG6" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-largest = nums[0]
+largest = nums[0]  # start from an actual value, not 0, so negatives work too
 for x in nums[1:]:
     if x &gt; largest:
         largest = x
@@ -1389,20 +1351,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-The library keeps issued-book IDs in a sorted list so lookups stay fast, and Sameer wants his search program to fail loudly if the list ever arrives unsorted — a perfect job for assert. Write a program that reads a line of sorted numbers and then a target. First use assert to confirm each number is at least as large as the one before it, then print 'Found' if the target is present and 'Not Found' otherwise.
-### Input Format
-- Line 1: Sorted space-separated numbers
-- Line 2: Target
-### Output Format
-```
-Found
-```
+          <t>The library keeps issued-book IDs in a sorted list so lookups stay fast, and Sameer wants his search program to fail loudly if the list ever arrives unsorted — a perfect job for assert. Write a program that reads a line of sorted numbers and then a target. First use assert to confirm each number is at least as large as the one before it, then print 'Found' if the target is present and 'Not Found' otherwise.
 ### Example Walkthrough
 The list `1 2 3 4 5` passes the sorted check, since each value is at least as large as the one before it. The target 3 does appear in the list, so the program prints `Found`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1542,7 +1496,7 @@
       <c r="AG7" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-assert nums == sorted(nums), "list must be sorted"
+assert nums == sorted(nums), "list must be sorted"  # fail loudly if the input breaks the sorted assumption
 target = int(input())
 print("Found" if target in nums else "Not Found")</t>
         </is>
@@ -1556,19 +1510,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-On the bus ride home, Ritu and her friends play a game: a ticket number is 'lucky' if it reads the same forwards and backwards, like 121. Write a program that reads a whole number and prints 'Yes' if its digits form such a palindrome, and 'No' otherwise. A single-digit number always counts as a palindrome.
-### Input Format
-- Line 1: A whole number
-### Output Format
-```
-Yes
-```
+          <t>On the bus ride home, Ritu and her friends play a game: a ticket number is 'lucky' if it reads the same forwards and backwards, like 121. Write a program that reads a whole number and prints 'Yes' if its digits form such a palindrome, and 'No' otherwise. A single-digit number always counts as a palindrome.
 ### Example Walkthrough
 The sample number 121 read backwards is still 121 — the first and last digits are both 1 and the middle digit stays 2 — so the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1701,7 +1648,7 @@
       <c r="AG8" t="inlineStr">
         <is>
           <t>n = input().strip()
-print("Yes" if n == n[::-1] else "No")</t>
+print("Yes" if n == n[::-1] else "No")  # compare the string to its reverse</t>
         </is>
       </c>
     </row>
@@ -1713,20 +1660,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-In the mess kitchen, clean plates are stacked up: 'push' places a plate on top and 'pop' takes one off. Taking a plate from an empty stack is impossible, and Arnav wants an assert to guarantee his simulation never tries it. Write a program that reads N and then N operations ('push' or 'pop'). Use assert to check the stack is not empty before every pop (the input is well-formed), then print how many plates remain at the end.
-### Input Format
-- Line 1: N
-- Next N lines: 'push' or 'pop'
-### Output Format
-```
-2
-```
+          <t>In the mess kitchen, clean plates are stacked up: 'push' places a plate on top and 'pop' takes one off. Taking a plate from an empty stack is impossible, and Arnav wants an assert to guarantee his simulation never tries it. Write a program that reads N and then N operations ('push' or 'pop'). Use assert to check the stack is not empty before every pop (the input is well-formed), then print how many plates remain at the end.
 ### Example Walkthrough
 The 4 sample operations are push, push, pop, push. The plate count goes 1, 2, back down to 1, then up to 2 — and no pop ever hits an empty stack — so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1886,7 +1825,7 @@
     if op == "push":
         size += 1
     else:
-        assert size &gt; 0, "cannot pop empty stack"
+        assert size &gt; 0, "cannot pop empty stack"  # guard the invariant before popping
         size -= 1
 print(size)</t>
         </is>
@@ -1902,19 +1841,11 @@
         <is>
           <t>A ticket-numbering script should print every ticket number from 1 to N, one per line, but a common off-by-one bug is writing the loop as `range(1, n)`, which stops one short and misses ticket N entirely. Write the correct version.
 Write a program that reads a whole number N and prints every whole number from 1 to N, inclusive, one per line, using `range(1, n + 1)`. If N is 0 or less, print nothing.
-### Input Format
-- Line 1: N
-### Output Format
-```
-1
-2
-3
-```
 ### Example Walkthrough
 In the sample, N is 3. The correct range `range(1, 4)` produces 1, 2, and 3, so the program prints all three, including the final ticket number 3 that the buggy `range(1, 3)` would have missed.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2064,7 +1995,7 @@
       <c r="AG10" t="inlineStr">
         <is>
           <t>n=int(input())
-for i in range(1,n+1): print(i)</t>
+for i in range(1,n+1): print(i)  # range(1, n+1) includes n, unlike range(1, n)</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2009,11 @@
         <is>
           <t>A grading script computes the class average from a list of scores, but a common bug is dividing the sum by the wrong count, such as a hardcoded number of students, instead of the actual number of scores that were entered. Write the correct version.
 Write a program that reads a line of space-separated numbers and prints their average, computed as the sum of the numbers divided by exactly how many numbers were entered.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-2.0
-```
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3`. Their sum is 6 and there are 3 of them, so the average is 6 / 3 = 2.0, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2220,514 +2145,314 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>nums=list(map(int,input().split())); print(sum(nums)/len(nums))</t>
+          <t>nums=list(map(int,input().split())); print(sum(nums)/len(nums))  # divide by len(nums), the real count, not a hardcoded number</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Python - Max Subarray Sum</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-Dhruv tracks his cricket team's net runs per over — positive when they scored freely, negative when wickets fell cheaply — and wants to find the team's best stretch of consecutive overs. Write a program that reads a line of numbers (which may be negative) and prints the largest sum of any run of one or more consecutive numbers.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-6
-```
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dhruv tracks his cricket team's net runs per over — positive when they scored freely, negative when wickets fell cheaply — and wants to find the team's best stretch of consecutive overs. Write a program that reads a line of numbers (which may be negative) and prints the largest sum of any run of one or more consecutive numbers.
 ### Example Walkthrough
 In `-2 1 -3 4 -1 2 1 -5 4`, the best consecutive stretch is `4 -1 2 1`, which adds up to 6. No other run of neighbouring numbers does better, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>-2 1 -3 4 -1 2 1 -5 4</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>-1 2 -1 2 -1</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-best = current = nums[0]
+best = current = nums[0]  # start both trackers at the first element
 for x in nums[1:]:
-    current = max(x, current + x)
-    best = max(best, current)
+    current = max(x, current + x)  # either extend the current run or start fresh here
+    best = max(best, current)  # remember the best run seen so far
 print(best)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Python - Leap Year Rules</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-Zara's cousin was born on 29 February, so his 'real' birthday only arrives in a leap year — and Zara's first program got years like 1900 wrong. Implement the full rules yourself (a common source of bugs): a year is a leap year if it is divisible by 4, except that years divisible by 100 are not, unless they are also divisible by 400. Read a year and print 'Yes' or 'No'.
-### Input Format
-- Line 1: A year
-### Output Format
-```
-Yes
-```
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Zara's cousin was born on 29 February, so his 'real' birthday only arrives in a leap year — and Zara's first program got years like 1900 wrong. Implement the full rules yourself (a common source of bugs): a year is a leap year if it is divisible by 4, except that years divisible by 100 are not, unless they are also divisible by 400. Read a year and print 'Yes' or 'No'.
 ### Example Walkthrough
 2000 is divisible by 4, and also by 100 — which would normally disqualify it — but it is divisible by 400 too, so the exception-to-the-exception applies and the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>1900</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>2100</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>year = int(input())
 if year % 400 == 0:
-    leap = True
+    leap = True  # exception to the exception: centuries divisible by 400 ARE leap years
 elif year % 100 == 0:
-    leap = False
+    leap = False  # centuries are not leap years unless divisible by 400 (checked above)
 elif year % 4 == 0:
     leap = True
 else:
@@ -2736,1751 +2461,1505 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Python - Sum of Inclusive Range</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read A and B and print the sum of every whole number from A to B, including both A and B.
-### Input Format
-- Line 1: 'A B'
-### Output Format
-```
-15
-```
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A fitness app lets participants log a walking challenge and total up the steps recorded from day A through day B, but the running total was quietly skipping day B because the loop stopped one day early. Read A and B and print the sum of every whole number from A to B, including both A and B.
 ### Example Walkthrough
 In the sample, `A` is `1` and `B` is `5`. Summing every whole number from `1` to `5` gives `15`, so the program prints `15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>1 5</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>3 3</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1 10</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>-5 -1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>-3 3</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>a, b = map(int, input().split())
-print(sum(range(a, b + 1)))</t>
+print(sum(range(a, b + 1)))  # +1 so b itself is included in the sum</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Python - Last Valid Index</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>A list of length n has valid indexes 0 to n-1. Read a line of values and print the last valid index.
-### Input Format
-- Line 1: Space-separated values
-### Output Format
-```
-2
-```
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A warehouse inventory app stores each shelf's items in a list, and a bug made the app try to read one position past the end of the list whenever a worker checked the last item on the shelf. A list of length n has valid indexes 0 to n-1, so read a line of items and print the last valid index.
 ### Example Walkthrough
-In the sample, the values are `a b c`. With `3` items, the valid indexes are `0`, `1`, and `2`, so the program prints `2`.
+In the sample, the values are `1 2 3`. With `3` items, the valid indexes are `0`, `1`, and `2`, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>-1 -2</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>a b c d</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>items = input().split()
-print(len(items) - 1)</t>
+print(len(items) - 1)  # last valid index is length minus one, since indexing starts at 0</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Python - Boundary Pass Mark</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>The pass mark is 40 and exactly 40 passes. Read a score and print 'Pass' if it is 40 or more, otherwise 'Fail'.
-### Input Format
-- Line 1: A score
-### Output Format
-```
-Pass
-```
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A school's exam-results app was marking students who scored exactly the pass mark as failures, because the comparison only checked for scores strictly above 40. The pass mark is 40 and exactly 40 passes, so read a score and print 'Pass' if it is 40 or more, otherwise 'Fail'.
 ### Example Walkthrough
 In the sample, the score is exactly `40`, the pass mark itself. Since `40 &gt;= 40`, the program prints `Pass`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>score = int(input())
-print("Pass" if score &gt;= 40 else "Fail")</t>
+print("Pass" if score &gt;= 40 else "Fail")  # &gt;= so exactly 40 counts as a pass</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Python - Count Up Correctly</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Print every number from 1 to N, including N, separated by spaces (getting the loop bounds right).
-### Input Format
-- Line 1: N
-### Output Format
-```
-1 2 3 4 5
-```
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A gym workout app counts out loud from 1 up to the target number of reps, but a loop bound bug meant the final rep, the one that matters most, was never announced. Print every number from 1 to N, including N, separated by spaces.
 ### Example Walkthrough
 In the sample, `N` is `5`. Counting up to and including `5` gives `1 2 3 4 5`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>n = int(input())
-print(*range(1, n + 1))</t>
+print(*range(1, n + 1))  # +1 so n itself is included in the range</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Python - Equal or Larger</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Read two numbers. Print 'Equal' if they are equal; otherwise print the larger one. (Watch the boundary where they are equal.)
-### Input Format
-- Line 1: 'a b'
-### Output Format
-```
-Equal
-```
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A shopping price-comparison app checks two listings for the same product and should flag a tie when both prices match, but a careless comparison meant equal prices always got reported as one price being 'larger'. Read two numbers and print 'Equal' if they are equal; otherwise print the larger one.
 ### Example Walkthrough
-In the sample, both numbers are `5`. Since they are equal, the program prints `Equal` rather than either value.
+In the sample, both numbers are `3`. Since they are equal, the program prints `Equal` rather than either value.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>3 3</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>5 2</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>1 4</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>-5 -5</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>-1 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>100 99</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>a, b = map(int, input().split())
 if a == b:
-    print("Equal")
+    print("Equal")  # handle the equal boundary before comparing sizes
 else:
     print(max(a, b))</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Python - Assert Non-Empty</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Read a word. Use an assert to confirm it is not empty, then print its first character.
-### Input Format
-- Line 1: A non-empty word
-### Output Format
-```
-h
-```
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A student-feedback app peeks at the first character of each response to sort it into a category, but it would crash with an ugly traceback whenever someone submitted a blank response. Read a word, use an assert to confirm it is not empty, then print its first character.
 ### Example Walkthrough
 In the sample, the word is `hello`, which is not empty, so the assert passes and the program prints its first character, `h`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>assertions</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>xyz</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>world</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>w</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>banana</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>word = input()
-assert len(word) &gt; 0, "word must not be empty"
+assert len(word) &gt; 0, "word must not be empty"  # fail loudly before indexing into an empty string
 print(word[0])</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Python - Assert Positive</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A configuration loader uses an assertion to guarantee that a setting value is a positive number before continuing, catching the resulting `AssertionError` to report a friendly message instead of letting the program crash with a raw traceback.
 Write a program that reads a whole number inside a `try` block, uses `assert n &gt; 0` to check it is positive, and prints `OK` if the assertion passes. If the assertion fails, catch the `AssertionError` and print `Not positive`.
-### Input Format
-- Line 1: A whole number
-### Output Format
-```
-OK
-```
 ### Example Walkthrough
 In the sample, the number is 1, which is positive, so the assertion passes and the program prints `OK`. A value of `0` or lower would fail the assertion and print `Not positive` instead.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>assertions</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Not positive</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Not positive</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>Not positive</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>try:
- n=int(input()); assert n&gt;0; print("OK")
-except AssertionError: print("Not positive")</t>
+ n=int(input()); assert n&gt;0; print("OK")  # assert raises AssertionError when n is not positive
+except AssertionError: print("Not positive")  # catch it and show a friendly message instead of crashing</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Python - Boundary Pass Fix</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A results checker marks students as passing at exactly 40 marks or above, but a common bug is using `&gt;` instead of `&gt;=`, which would incorrectly fail a student who scored exactly 40. Write the correct version.
 Write a program that reads a whole number of marks and prints `Pass` if the marks are 40 or more (using `&gt;=`, so exactly 40 counts as a pass), and `Fail` otherwise.
-### Input Format
-- Line 1: Marks
-### Output Format
-```
-Pass
-```
 ### Example Walkthrough
 In the sample, the marks are exactly 40. Using `&gt;=`, 40 is greater than or equal to 40, so the program prints `Pass`, unlike a buggy `&gt;` check which would have incorrectly printed `Fail`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>m=int(input()); print("Pass" if m&gt;=40 else "Fail")</t>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>m=int(input()); print("Pass" if m&gt;=40 else "Fail")  # &gt;= so exactly 40 counts as a pass, not just above it</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Python - Correct Percentage</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Read marks obtained and the total marks, and print the percentage rounded to 1 decimal place (avoiding the integer-division bug).
-### Input Format
-- Line 1: 'obtained total'
-### Output Format
-```
-90.0
-```
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>An online certification portal shows candidates their score as a percentage right after a test, but an integer-division bug was truncating the decimal part and displaying the wrong result. Read marks obtained and the total marks, and print the percentage rounded to 1 decimal place.
 ### Example Walkthrough
-In the sample, the marks obtained are `90` out of `100`. The percentage is `90 / 100 x 100 = 90.0`, so the program prints `90.0`.
+In the sample, the marks obtained are `45` out of `50`. The percentage is `45 / 50 x 100 = 90.0`, so the program prints `90.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>45 50</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>1 3</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>33.3</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>50 50</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>0 50</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>50 200</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>33 99</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>33.3</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>obtained, total = map(int, input().split())
-print(round(obtained / total * 100, 1))</t>
+print(round(obtained / total * 100, 1))  # true division keeps decimals, avoiding the integer-division bug</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Python - Grade Boundaries</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Read a mark and print its grade using inclusive boundaries: 'A' for 90 or more, 'B' for 75 or more, 'C' for 60 or more, and 'F' otherwise. Check the exact boundary values.
-### Input Format
-- Line 1: A mark
-### Output Format
-```
-A
-```
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A college's grading system was quietly bumping students at the exact cutoff down to the lower grade, because the boundary checks used strict comparisons instead of inclusive ones. Read a mark and print its grade using inclusive boundaries: 'A' for 90 or more, 'B' for 75 or more, 'C' for 60 or more, and 'F' otherwise.
 ### Example Walkthrough
 In the sample, the mark is exactly `90`, the boundary for an `A`. Since `90 &gt;= 90`, the program prints `A`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>marks = int(input())
 if marks &gt;= 90:
-    print("A")
+    print("A")  # &gt;= makes the boundary value itself count for the higher grade
 elif marks &gt;= 75:
     print("B")
 elif marks &gt;= 60:
@@ -4490,628 +3969,604 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Python - Sum of Squares</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>A buggy version adds the numbers instead of their squares. Read a line of numbers and print the sum of their squares.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-14
-```
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A fantasy sports league scores players by the square of their performance rating, but a bug in the scoring app was just adding up the raw ratings instead of squaring them first. Read a line of numbers and print the sum of their squares.
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3`. Their squares are `1`, `4`, and `9`, which sum to `14`, so the program prints `14`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>2 4</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>-3 3</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>-1 -2 -3</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-print(sum(x * x for x in nums))</t>
+print(sum(x * x for x in nums))  # square each value before summing, not the raw numbers</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Python - Above Average Count</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read a line of numbers and print how many of them are strictly greater than the average of the list.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-2
-```
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A class-analytics tool highlights which students scored above the class average on a test, but the teacher noticed the count looked off after trying it on a real gradebook. Read a line of numbers and print how many of them are strictly greater than the average of the list.
 ### Example Walkthrough
-In the sample, the numbers are `1 2 3 4 5`, with an average of `3`. The values `4` and `5` are strictly greater than `3`, so the program prints `2`.
+In the sample, the numbers are `1 2 3 4`, with an average of `2.5`. The values `3` and `4` are strictly greater than `2.5`, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>1 10</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>-5 -1 5</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>1 1 1 1 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-average = sum(nums) / len(nums)
-print(sum(1 for x in nums if x &gt; average))</t>
+average = sum(nums) / len(nums)  # true division so the average keeps its decimal part
+print(sum(1 for x in nums if x &gt; average))  # strictly greater than average, ties do not count</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Python - Reverse Without Loss</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read a line of values and print them reversed, making sure not to drop the first or last element.
-### Input Format
-- Line 1: Space-separated values
-### Output Format
-```
-3 2 1
-```
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A messaging app's playful 'mirror text' feature flips a message back to front, but a slicing bug was silently dropping the first and last characters of every message it reversed. Read a line of values and print them reversed, making sure not to drop the first or last element.
 ### Example Walkthrough
 In the sample, the values are `1 2 3`. Reversed, they become `3 2 1`, which the program prints, keeping both the first and last elements.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>3 2 1</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>2 1</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>5 4 3 2 1</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>x y</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>y x</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>9 8 7 6</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>6 7 8 9</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>items = input().split()
-print(*items[::-1])</t>
+print(*items[::-1])  # step -1 reverses the list without dropping either end</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Python - Smallest Gap</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read a line of numbers, sort them, and print the smallest difference between any two neighbouring values in the sorted order.
-### Input Format
-- Line 1: Space-separated numbers (at least two)
-### Output Format
-```
-0
-```
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A college scheduling app lists the start times of back-to-back lectures and needs to flag the two that are scheduled closest together, so a coordinator can catch clashes early. Read a line of numbers, sort them, and print the smallest difference between any two neighbouring values in the sorted order.
 ### Example Walkthrough
-In the sample, the numbers are `1 1 3`. Sorted, they are `1, 1, 3`, and the gaps between neighbours are `0` and `2`. The smallest gap is `0`, so the program prints `0`.
+In the sample, the numbers are `3 1 4 1 5`. Sorted, they become `1, 1, 3, 4, 5`, and the gaps between neighbours are `0`, `2`, `1`, and `1`. The smallest gap is `0`, so the program prints `0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>3 1 4 1 5</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>10 20 30</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>5 8</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>-5 5</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>-10 -3 -7</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>0 0 0</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>nums = sorted(map(int, input().split()))
-smallest = nums[1] - nums[0]
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>nums = sorted(map(int, input().split()))  # sort first so neighbours are the closest pairs
+smallest = nums[1] - nums[0]  # start from the first real gap, not 0, so it can only shrink
 for i in range(1, len(nums)):
     gap = nums[i] - nums[i - 1]
     if gap &lt; smallest:
@@ -5120,562 +4575,537 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Python - Assert Valid Marks</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Read a line of marks. Use an assert to confirm every mark is between 0 and 100, then print their average rounded to 1 decimal place.
-### Input Format
-- Line 1: Space-separated marks (each 0 to 100)
-### Output Format
-```
-90.0
-```
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A result-verification tool double-checks a set of marks before they get published, using an assert as a safety net to catch any mark that has slipped outside the valid 0-100 range due to a data-entry error. Read a line of marks, use an assert to confirm every mark is between 0 and 100, then print their average rounded to 1 decimal place.
 ### Example Walkthrough
-In the sample, the marks are `90 90 90`, all within `0` to `100`, so the assert passes and the average, `90.0`, is printed.
+In the sample, the marks are `80 90 100`, all within `0` to `100`, so the assert passes and the average, `90.0`, is printed.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>assertions</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>80 90 100</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>0 100</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>60 70 80 90</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>marks = list(map(int, input().split()))
-assert all(0 &lt;= m &lt;= 100 for m in marks), "marks out of range"
+assert all(0 &lt;= m &lt;= 100 for m in marks), "marks out of range"  # fail loudly if any mark is out of bounds
 print(round(sum(marks) / len(marks), 1))</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Python - Sorted Assertion</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A leaderboard update script assumes an incoming list of scores is already sorted before merging it with the existing leaderboard, and uses an assertion to immediately catch the moment that assumption is violated instead of silently producing a broken leaderboard.
 Write a program that reads a line of space-separated whole numbers inside a `try` block, uses `assert nums == sorted(nums)` to check the list is sorted from smallest to largest, and prints `Sorted` if the assertion passes. If it fails, catch the `AssertionError` and print `Not sorted`.
-### Input Format
-- Line 1: Space-separated whole numbers
-### Output Format
-```
-Sorted
-```
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3`, which are already in increasing order, so the assertion passes and the program prints `Sorted`. Numbers like `3 2 1` would fail the assertion and print `Not sorted` instead.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>assertions</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>Sorted</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>3 2 1</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Not sorted</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>1 1 2</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Sorted</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Sorted</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>-1 0 1</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>Sorted</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>1 3 2</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>Not sorted</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>0 0 0</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>Sorted</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>nums=list(map(int,input().split()))
-try: assert nums==sorted(nums); print("Sorted")
-except AssertionError: print("Not sorted")</t>
+try: assert nums==sorted(nums); print("Sorted")  # assert fails if the list is not already sorted
+except AssertionError: print("Not sorted")  # catch the failure and report it instead of crashing</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Python - First Zero Trace</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>A sensor log analyzer needs to find the position of the first zero reading in a batch, since a zero often indicates the sensor briefly disconnected, so an engineer traces through the values to find the index of the first occurrence, or -1 if none of the readings were zero.
 Write a program that reads a line of space-separated whole numbers and prints the index (starting at 0) of the first value equal to 0. If no value is 0, print `-1`.
-### Input Format
-- Line 1: Space-separated whole numbers
-### Output Format
-```
-1
-```
 ### Example Walkthrough
 In the sample, the readings are `1 0 2`. The first 0 appears at index 1 (the second position, counting from 0), so the program prints `1`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>debugging-workflow</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>1 0 2</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>5 4 0 0</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>-1 0</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>9 8 7</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>0 1 0</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>ans=-1
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>ans=-1  # default to -1, meaning no zero was found
 for i,x in enumerate(map(int,input().split())):
- if x==0: ans=i; break
+ if x==0: ans=i; break  # record the index and stop at the first zero
 print(ans)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Python - Logging Level Count</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>A log-monitoring dashboard scans a batch of log entries and counts exactly how many are tagged with the level `ERROR` (matching the exact case used by the logging system, so `error` in lower case does not count), so it can flag a spike in errors.
 Write a program that reads a whole number N, then reads N more lines each containing a log level, and prints how many of them are exactly `ERROR`.
-### Input Format
-- Line 1: N, the number of log entries
-- Next N lines: a log level each
-### Output Format
-```
-2
-```
 ### Example Walkthrough
 In the sample, N is 3 with the levels `INFO`, `ERROR`, and `ERROR`. Two of the three entries are exactly `ERROR`, so the program prints `2`.
 ### Constraints
 - N is a valid whole number matching the number of lines that follow.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>logging</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>3
 INFO
@@ -5683,45 +5113,45 @@
 ERROR</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>1
 INFO</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>2
 ERROR
 WARN</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>4
 ERROR
@@ -5730,391 +5160,198 @@
 INFO</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>2
 error
 ERROR</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>1
 ERROR</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>n=int(input()); c=0
 for _ in range(n):
- if input()=="ERROR": c+=1
+ if input()=="ERROR": c+=1  # exact case match, "error" in lower case would not count
 print(c)</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Python - Pair Sum Exists</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Read a sorted line of numbers and a target. Print 'Yes' if some pair of different positions adds up to the target, otherwise 'No'. Use two indexes moving inward and mind the boundaries.
-### Input Format
-- Line 1: Sorted space-separated numbers
-- Line 2: Target
-### Output Format
-```
-Yes
-```
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A bank's fraud-detection tool scans a sorted list of transaction amounts to see if any two of them add up to a suspicious flagged total, using two pointers that move inward from both ends. Read a sorted line of numbers and a target, and print 'Yes' if some pair of different positions adds up to the target, otherwise 'No'.
 ### Example Walkthrough
-In the sample, the numbers are `1 2 3 4 5` and the target is `6`. The pair `1` and `5` adds up to `6`, so the program prints `Yes`.
+In the sample, the numbers are `1 2 3 4` and the target is `5`. The pair `1` and `4` adds up to `5`, so the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>1 2 3 4
 5</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>1 2 3
 7</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>2 4
 6</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>1 2
 3</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>-5 -1 0 3
 -6</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6
 11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>-3 -2 -1
 -3</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 target = int(input())
-left, right = 0, len(nums) - 1
+left, right = 0, len(nums) - 1  # two pointers starting at both ends of the sorted list
 found = False
 while left &lt; right:
     total = nums[left] + nums[right]
@@ -6122,176 +5359,169 @@
         found = True
         break
     elif total &lt; target:
-        left += 1
+        left += 1  # sum too small, move the left pointer up to increase it
     else:
-        right -= 1
+        right -= 1  # sum too big, move the right pointer down to decrease it
 print("Yes" if found else "No")</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Python - Max Window Sum</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Read a line of numbers and a window size K. Print the largest sum of any K consecutive numbers. Take care that the last window is included.
-### Input Format
-- Line 1: Space-separated numbers
-- Line 2: K
-### Output Format
-```
-9
-```
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A stock-analysis tool scans a run of daily price changes to find the best K-day stretch to have held the stock, but a boundary bug meant the very last possible window of days was never checked. Read a line of numbers and a window size K, and print the largest sum of any K consecutive numbers.
 ### Example Walkthrough
-In the sample, the numbers are `4 5` and `K` is `2`. The only window of size `2` sums to `4 + 5 = 9`, so the program prints `9`.
+In the sample, the numbers are `1 2 3 4 5` and `K` is `2`. The best window of size `2` is the last one, `4` and `5`, which sums to `9`, so the program prints `9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 2</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>5 1 1
 1</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>2 2 2
 3</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>-1 -2 -3
 1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>5
 1</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>1 2 3 4
 4</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>-5 10 -3 8
 2</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 k = int(input())
-best = sum(nums[:k])
-for i in range(1, len(nums) - k + 1):
+best = sum(nums[:k])  # sum of the first window
+for i in range(1, len(nums) - k + 1):  # +1 so the last possible window is included
     window = sum(nums[i:i + k])
     if window &gt; best:
         best = window
@@ -6299,638 +5529,614 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Python - Careful Rounding</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Floating-point sums can look wrong (0.1 + 0.2 is not exactly 0.3). Read a line of decimal amounts and print their total rounded to 2 decimal places.
-### Input Format
-- Line 1: Space-separated decimal numbers
-### Output Format
-```
-0.3
-```
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A billing app totals up several decimal payments before showing a customer their final amount, but raw floating-point addition kept displaying odd values like 0.30000000000000004 instead of a clean total. Read a line of decimal amounts and print their total rounded to 2 decimal places.
 ### Example Walkthrough
 In the sample, the amounts are `0.1` and `0.2`. Their sum, rounded to 2 decimal places, is `0.3`, so the program prints `0.3` even though raw floating-point addition can look slightly off.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>0.1 0.2</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>1.5 2.5</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>0.01 0.02</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>-1.5 1.5</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>10.999 0.001</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>-0.1 -0.2</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>-0.3</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>amounts = list(map(float, input().split()))
-print(round(sum(amounts), 2))</t>
+print(round(sum(amounts), 2))  # round at the end to hide floating-point representation error</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Python - Count All Vowels</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>A buggy counter resets between words and loses the total. Read a sentence and print the total number of vowels across the whole sentence, ignoring case.
-### Input Format
-- Line 1: A sentence
-### Output Format
-```
-4
-```
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A speech-analysis app counts vowel sounds across a transcribed sentence to gauge how clearly someone is speaking, but a bug was resetting the tally to zero at the start of every new word, losing the running total. Read a sentence and print the total number of vowels across the whole sentence, ignoring case.
 ### Example Walkthrough
-In the sample, the sentence is `the quick fox`. It contains `4` vowels (`e`, `u`, `i`, `o`), so the program prints `4`.
+In the sample, the sentence is `the quick brown`. It contains `4` vowels (`e`, `u`, `i`, `o`), so the program prints `4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>the quick brown</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>aeiou</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>xyz</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>AEIOU</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>b c d</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>Hello World</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>sentence = input().lower()
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>sentence = input().lower()  # lowercase once so the vowel check ignores case
 count = 0
 for ch in sentence:
     if ch in "aeiou":
-        count += 1
+        count += 1  # one running total across the whole sentence, not reset per word
 print(count)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Python - First Repeated Value</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read a line of numbers and print the first value whose second occurrence appears earliest as you scan left to right. If nothing repeats, print 'None'.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-2
-```
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A plagiarism checker scans a sequence of submission IDs and wants to catch the first one that has clearly been reused, reporting whichever ID gets flagged as a repeat earliest while scanning left to right. Read a line of numbers and print the first value whose second occurrence appears earliest as you scan left to right. If nothing repeats, print 'None'.
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3 2 1`. Scanning left to right, `2` is the first value seen a second time, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>1 2 3 2 1</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>5 6 7</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>4 4</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>-3 -3</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>9 8 7 6 8</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>nums = input().split()
 seen = set()
-answer = "None"
+answer = "None"  # default when nothing repeats
 for x in nums:
     if x in seen:
-        answer = x
+        answer = x  # first value seen a second time while scanning left to right
         break
     seen.add(x)
 print(answer)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Python - Assert Then Factorial</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read a number. Use an assert to confirm it is not negative (factorial is undefined for negatives), then compute and print its factorial.
-### Input Format
-- Line 1: A number
-### Output Format
-```
-120
-```
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A math-puzzle app lets players compute the factorial of any number they type in, but it needs an assert as a guard rail since factorial has no meaning for negative numbers and would otherwise misbehave. Read a number, use an assert to confirm it is not negative, then compute and print its factorial.
 ### Example Walkthrough
 In the sample, the number is `5`, which is not negative, so the assert passes and the program prints `5! = 120`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>assertions</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>3628800</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>n = int(input())
-assert n &gt;= 0, "factorial needs a non-negative number"
+assert n &gt;= 0, "factorial needs a non-negative number"  # factorial is undefined for negatives
 result = 1
 for i in range(2, n + 1):
     result *= i
@@ -6938,160 +6144,154 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Python - Collatz Steps</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Read a number and count how many steps it takes to reach 1 using the Collatz process: if the number is even, halve it; if odd, triple it and add one. Print the number of steps (0 if the number is already 1).
-### Input Format
-- Line 1: A positive whole number
-### Output Format
-```
-8
-```
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A number-theory puzzle app challenges students to trace the Collatz conjecture for any starting number and count how many steps it takes to spiral down to 1. Read a number and count how many steps it takes to reach 1 using the Collatz process: if the number is even, halve it; if odd, triple it and add one. Print the number of steps (0 if the number is already 1).
 ### Example Walkthrough
 In the sample, the number is `6`. Following the Collatz process gives `6, 3, 10, 5, 16, 8, 4, 2, 1`, which takes `8` steps to reach `1`, so the program prints `8`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>n = int(input())
 steps = 0
-while n != 1:
+while n != 1:  # keep applying the rule until we reach 1
     if n % 2 == 0:
         n //= 2
     else:
@@ -7101,501 +6301,480 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Python - Off By One Window</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>A stock-analysis tool finds the best K-day rolling sum of daily profits to spot the strongest short streak, sliding a window of size K across the data. A common off-by-one bug stops the sliding window one position too early and misses the very last possible window; write the correct version.
 Write a program that reads a line of space-separated whole numbers, reads a whole number K on the next line, and prints the maximum sum of any K consecutive numbers in the list, making sure to check every possible window including the last one.
-### Input Format
-- Line 1: Space-separated whole numbers
-- Line 2: K, the window size
-### Output Format
-```
-7
-```
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3 4` and K is 2. The possible windows of size 2 are `1+2=3`, `2+3=5`, and `3+4=7`; the largest is 7, so the program prints `7`.
 ### Constraints
 - K is a valid whole number no greater than the number of values given.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>debugging-techniques</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>1 2 3 4
 2</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>5
 1</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>1 2 3
 3</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>-1 -2 -3
 2</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>10 0 10
 2</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>1 1 1 1
 3</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>5 4 3 2 1
 2</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>nums=list(map(int,input().split())); k=int(input()); best=sum(nums[:k])
-for i in range(1,len(nums)-k+1): best=max(best,sum(nums[i:i+k]))
+for i in range(1,len(nums)-k+1): best=max(best,sum(nums[i:i+k]))  # +1 so the last window is not skipped
 print(best)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Python - Invariant Stack</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>A browser's back-button history is modeled as a stack of push and pop operations coming from user navigation actions. The invariant that must always hold is that you can't pop when the stack is empty (you can't go back further than the history allows), so the app validates a sequence of operations to check whether it ever breaks that rule.
 Write a program that reads a line of space-separated operations (`push` or `pop`), simulates them on a stack, and prints `OK` if every `pop` had something to remove, or `Broken` the moment a `pop` is attempted on an empty stack.
-### Input Format
-- Line 1: Space-separated operations (`push` or `pop`)
-### Output Format
-```
-OK
-```
 ### Example Walkthrough
 In the sample, the operations are `push pop`. The `push` adds an item, and the `pop` removes it since the stack wasn't empty, so the invariant holds and the program prints `OK`.
 ### Constraints
 - The input is a valid line of space-separated operations, each either `push` or `pop`.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>assertions</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>push pop</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Broken</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>push push pop</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>push pop pop</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Broken</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>push push pop pop</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>push</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>push pop push pop</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>ops=input().split(); stack=[]; ok=True
 for op in ops:
  if op=="push": stack.append(1)
  elif op=="pop":
-  if not stack: ok=False; break
+  if not stack: ok=False; break  # popping an empty stack breaks the invariant
   stack.pop()
 print("OK" if ok else "Broken")</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Python - Rubber Duck Trace</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>While rubber-duck debugging a budgeting script, a developer traces through it line by line: for each new expense added, print the running total so far immediately, to see exactly where the total starts to go wrong.
 Write a program that reads a line of space-separated whole numbers and, keeping a running total, prints the total after adding each number, one line per number.
-### Input Format
-- Line 1: Space-separated whole numbers
-### Output Format
-```
-1
-3
-6
-```
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3`. After adding 1, the running total is 1; after adding 2, it becomes 3; after adding 3, it becomes 6 - so the program prints `1`, then `3`, then `6`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>debugging-workflow</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>1
 3
 6</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>-1 1</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>-1
 0</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>0 0 0</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>0
 0
 0</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>10 -3 2</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>10
 7
 9</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>1 -2 -3</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>1
 -1
 -4</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>100 200</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>100
 300</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>total=0
 for x in map(int,input().split()):
- total+=x; print(total)</t>
+ total+=x; print(total)  # print immediately after each update to trace where totals diverge</t>
         </is>
       </c>
     </row>
